--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.159.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.159.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0159.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0159.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€” See Orders of 1850, under which pleadings need not</t>
+          <t>L34: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”The folio consists of 100 words.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]152</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]152</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L6: isolated marker/symbol line :: 50</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L18: symbol-only separator/garbage line :: .5 0</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]152</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,12 +668,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L37: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Office Copyâ€¢</t>
+          <t>L39: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Office Copy•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,7 +685,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: #</t>
+          <t>L18: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -723,12 +727,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L52: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”See Orders of 1850,under which pleadings need not</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -740,7 +744,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L99: symbol-only separator/garbage line :: 0 6</t>
+          <t>L86: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -766,12 +770,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -780,12 +784,12 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”It is submitted that, although it has not been done</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>L53: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -795,7 +799,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: .</t>
+          <t>L99: symbol-only separator/garbage line :: 0 6</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -835,12 +839,12 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -850,7 +854,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 13</t>
+          <t>L116: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -886,7 +890,11 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -897,7 +905,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L118: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -933,7 +941,11 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr"/>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -944,7 +956,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: I</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -991,7 +1003,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: %</t>
+          <t>L124: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1013,12 +1025,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1036,7 +1048,11 @@
           <t>L29: isolated marker/symbol line :: 100</t>
         </is>
       </c>
-      <c r="O10" s="1" t="inlineStr"/>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>L126: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr"/>
@@ -1061,7 +1077,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1099,12 +1115,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1119,7 +1135,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 0</t>
+          <t>L34: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1162,7 +1178,7 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 25</t>
+          <t>L35: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr"/>
@@ -1205,7 +1221,7 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 0</t>
+          <t>L37: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr"/>
@@ -1248,7 +1264,7 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 1</t>
+          <t>L38: isolated marker/symbol line :: 25</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr"/>
@@ -1291,7 +1307,7 @@
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: 3</t>
+          <t>L39: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr"/>
@@ -1334,7 +1350,7 @@
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L49: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr"/>
@@ -1365,7 +1381,7 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 1</t>
+          <t>L50: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr"/>
@@ -1396,7 +1412,7 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 0</t>
+          <t>L52: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr"/>
@@ -1427,7 +1443,7 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L59: symbol-only separator/garbage line :: 1 0</t>
+          <t>L53: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr"/>
@@ -1458,7 +1474,7 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 1</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr"/>
@@ -1489,7 +1505,7 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 0</t>
+          <t>L55: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr"/>
@@ -1520,7 +1536,7 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: +</t>
+          <t>L56: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr"/>
@@ -1551,7 +1567,7 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: 0</t>
+          <t>L58: isolated marker/symbol line :: ・</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr"/>
@@ -1582,7 +1598,7 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 6</t>
+          <t>L59: symbol-only separator/garbage line :: 1 0</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr"/>
@@ -1613,7 +1629,7 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: .</t>
+          <t>L60: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -1644,7 +1660,7 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 5</t>
+          <t>L61: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr"/>
@@ -1675,7 +1691,7 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 0</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr"/>
@@ -1706,7 +1722,7 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 5</t>
+          <t>L65: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr"/>
@@ -1737,7 +1753,7 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 0</t>
+          <t>L66: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr"/>
@@ -1768,7 +1784,7 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L67: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr"/>
@@ -1799,7 +1815,7 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 0</t>
+          <t>L68: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr"/>
@@ -1830,7 +1846,7 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 5</t>
+          <t>L69: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -1861,7 +1877,7 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 0</t>
+          <t>L70: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr"/>
@@ -1892,7 +1908,7 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 2</t>
+          <t>L89: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr"/>
@@ -1923,7 +1939,7 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 6</t>
+          <t>L90: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr"/>
@@ -1954,7 +1970,7 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 0</t>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -1985,7 +2001,7 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: 4</t>
+          <t>L94: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2016,7 +2032,7 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: 5</t>
+          <t>L95: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2047,7 +2063,7 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 0</t>
+          <t>L96: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2078,7 +2094,7 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: Â·</t>
+          <t>L98: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2109,7 +2125,7 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L109: symbol-only separator/garbage line :: 1 3</t>
+          <t>L99: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2140,7 +2156,7 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: 1</t>
+          <t>L101: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2171,7 +2187,7 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: 3</t>
+          <t>L102: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2202,7 +2218,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 0</t>
+          <t>L104: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2233,7 +2249,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: 1</t>
+          <t>L105: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2264,7 +2280,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: 2</t>
+          <t>L108: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2279,6 +2295,192 @@
       <c r="X47" s="1" t="inlineStr"/>
       <c r="Y47" s="1" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr"/>
+      <c r="B48" s="1" t="inlineStr"/>
+      <c r="C48" s="1" t="inlineStr"/>
+      <c r="D48" s="1" t="inlineStr"/>
+      <c r="E48" s="1" t="inlineStr"/>
+      <c r="F48" s="1" t="inlineStr"/>
+      <c r="G48" s="1" t="inlineStr"/>
+      <c r="H48" s="1" t="inlineStr"/>
+      <c r="I48" s="1" t="inlineStr"/>
+      <c r="J48" s="1" t="inlineStr"/>
+      <c r="K48" s="1" t="inlineStr"/>
+      <c r="L48" s="1" t="inlineStr"/>
+      <c r="M48" s="1" t="inlineStr"/>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>L109: symbol-only separator/garbage line :: 1 3</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr"/>
+      <c r="P48" s="1" t="inlineStr"/>
+      <c r="Q48" s="1" t="inlineStr"/>
+      <c r="R48" s="1" t="inlineStr"/>
+      <c r="S48" s="1" t="inlineStr"/>
+      <c r="T48" s="1" t="inlineStr"/>
+      <c r="U48" s="1" t="inlineStr"/>
+      <c r="V48" s="1" t="inlineStr"/>
+      <c r="W48" s="1" t="inlineStr"/>
+      <c r="X48" s="1" t="inlineStr"/>
+      <c r="Y48" s="1" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr"/>
+      <c r="B49" s="1" t="inlineStr"/>
+      <c r="C49" s="1" t="inlineStr"/>
+      <c r="D49" s="1" t="inlineStr"/>
+      <c r="E49" s="1" t="inlineStr"/>
+      <c r="F49" s="1" t="inlineStr"/>
+      <c r="G49" s="1" t="inlineStr"/>
+      <c r="H49" s="1" t="inlineStr"/>
+      <c r="I49" s="1" t="inlineStr"/>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
+      <c r="L49" s="1" t="inlineStr"/>
+      <c r="M49" s="1" t="inlineStr"/>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>L110: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr"/>
+      <c r="P49" s="1" t="inlineStr"/>
+      <c r="Q49" s="1" t="inlineStr"/>
+      <c r="R49" s="1" t="inlineStr"/>
+      <c r="S49" s="1" t="inlineStr"/>
+      <c r="T49" s="1" t="inlineStr"/>
+      <c r="U49" s="1" t="inlineStr"/>
+      <c r="V49" s="1" t="inlineStr"/>
+      <c r="W49" s="1" t="inlineStr"/>
+      <c r="X49" s="1" t="inlineStr"/>
+      <c r="Y49" s="1" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr"/>
+      <c r="B50" s="1" t="inlineStr"/>
+      <c r="C50" s="1" t="inlineStr"/>
+      <c r="D50" s="1" t="inlineStr"/>
+      <c r="E50" s="1" t="inlineStr"/>
+      <c r="F50" s="1" t="inlineStr"/>
+      <c r="G50" s="1" t="inlineStr"/>
+      <c r="H50" s="1" t="inlineStr"/>
+      <c r="I50" s="1" t="inlineStr"/>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
+      <c r="L50" s="1" t="inlineStr"/>
+      <c r="M50" s="1" t="inlineStr"/>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>L111: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr"/>
+      <c r="P50" s="1" t="inlineStr"/>
+      <c r="Q50" s="1" t="inlineStr"/>
+      <c r="R50" s="1" t="inlineStr"/>
+      <c r="S50" s="1" t="inlineStr"/>
+      <c r="T50" s="1" t="inlineStr"/>
+      <c r="U50" s="1" t="inlineStr"/>
+      <c r="V50" s="1" t="inlineStr"/>
+      <c r="W50" s="1" t="inlineStr"/>
+      <c r="X50" s="1" t="inlineStr"/>
+      <c r="Y50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="1" t="inlineStr"/>
+      <c r="C51" s="1" t="inlineStr"/>
+      <c r="D51" s="1" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr"/>
+      <c r="G51" s="1" t="inlineStr"/>
+      <c r="H51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr"/>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
+      <c r="L51" s="1" t="inlineStr"/>
+      <c r="M51" s="1" t="inlineStr"/>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>L118: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr"/>
+      <c r="P51" s="1" t="inlineStr"/>
+      <c r="Q51" s="1" t="inlineStr"/>
+      <c r="R51" s="1" t="inlineStr"/>
+      <c r="S51" s="1" t="inlineStr"/>
+      <c r="T51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="inlineStr"/>
+      <c r="V51" s="1" t="inlineStr"/>
+      <c r="W51" s="1" t="inlineStr"/>
+      <c r="X51" s="1" t="inlineStr"/>
+      <c r="Y51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>L122: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+      <c r="W52" s="1" t="inlineStr"/>
+      <c r="X52" s="1" t="inlineStr"/>
+      <c r="Y52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="1" t="inlineStr"/>
+      <c r="C53" s="1" t="inlineStr"/>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr"/>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr"/>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
+      <c r="L53" s="1" t="inlineStr"/>
+      <c r="M53" s="1" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>L123: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr"/>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr"/>
+      <c r="S53" s="1" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr"/>
+      <c r="V53" s="1" t="inlineStr"/>
+      <c r="W53" s="1" t="inlineStr"/>
+      <c r="X53" s="1" t="inlineStr"/>
+      <c r="Y53" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
